--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488294_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488294_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8293</v>
+        <v>4.0177</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5211</v>
+        <v>4.414</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6918</v>
+        <v>-0.3963</v>
       </c>
       <c r="G2" t="n">
         <v>3.6804</v>
@@ -610,13 +610,13 @@
         <v>3.5205</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6113</v>
+        <v>0.577</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0943</v>
+        <v>-0.2014</v>
       </c>
       <c r="U2" t="n">
-        <v>0.483</v>
+        <v>0.7784</v>
       </c>
       <c r="V2" t="n">
         <v>-2.8338</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7142</v>
+        <v>2.7689</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6116</v>
+        <v>2.6663</v>
       </c>
       <c r="F3" t="n">
         <v>0.1026</v>
@@ -688,10 +688,10 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3159</v>
+        <v>0.3706</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1131</v>
+        <v>-0.0584</v>
       </c>
       <c r="U3" t="n">
         <v>0.429</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2939</v>
+        <v>1.299</v>
       </c>
       <c r="E4" t="n">
-        <v>1.798</v>
+        <v>0.7171</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5041</v>
+        <v>0.5819</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9256</v>
+        <v>0.0964</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4352</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3608</v>
+        <v>0.8479</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0584</v>
+        <v>0.7401</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7989</v>
+        <v>-0.5455</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2595</v>
+        <v>1.2856</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.984</v>
+        <v>-0.6437</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3637</v>
+        <v>-0.206</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6203</v>
+        <v>-0.4377</v>
       </c>
       <c r="P4" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9224</v>
+        <v>-0.1685</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2773</v>
+        <v>-0.023</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1997</v>
+        <v>-0.1455</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9433</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.2304</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9441000000000001</v>
+        <v>2.0054</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.7749</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.9256</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3221</v>
+        <v>0.4352</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221</v>
+        <v>-1.3608</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9441000000000001</v>
+        <v>2.0584</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3221</v>
+        <v>1.7989</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6221</v>
+        <v>0.2595</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.984</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.3637</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.6203</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0699</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.908</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2125</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1205</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0842</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1491</v>
+        <v>0.3221</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2333</v>
+        <v>0.6221</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6579</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5234</v>
+        <v>0.3221</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1813</v>
+        <v>0.6221</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4263</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3743</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.052</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9187</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1512</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7675</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4665</v>
+        <v>-1.3152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4342</v>
+        <v>1.8502</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0964</v>
+        <v>-1.5663</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.1608</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8479</v>
+        <v>-1.4055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7401</v>
+        <v>-0.3313</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5455</v>
+        <v>0.1758</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2856</v>
+        <v>-0.5071</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6437</v>
+        <v>-1.235</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.206</v>
+        <v>-0.3366</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4377</v>
+        <v>-0.8984</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5668</v>
+        <v>0.619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2736</v>
+        <v>-0.0575</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2932</v>
+        <v>0.6765</v>
       </c>
       <c r="V7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.163</v>
+        <v>-1.0324</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8596</v>
+        <v>-0.664</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0226</v>
+        <v>-0.3684</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5663</v>
+        <v>0.3163</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1608</v>
+        <v>2.0827</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4055</v>
+        <v>-1.7664</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3313</v>
+        <v>3.2538</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1758</v>
+        <v>3.1388</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5071</v>
+        <v>0.115</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.235</v>
+        <v>-2.9375</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3366</v>
+        <v>-1.0561</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8984</v>
+        <v>-1.8814</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4823</v>
+        <v>-4.4469</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-6.485</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.247</v>
+        <v>0.581</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6019</v>
+        <v>0.0501</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8488</v>
+        <v>0.531</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.5172</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.5172</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6276</v>
+        <v>-1.0584</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2838</v>
+        <v>-1.3324</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3438</v>
+        <v>0.274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3163</v>
+        <v>0.8262</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0827</v>
+        <v>1.8338</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7664</v>
+        <v>-1.0076</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2538</v>
+        <v>1.4699</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1388</v>
+        <v>2.0398</v>
       </c>
       <c r="L9" t="n">
-        <v>0.115</v>
+        <v>-0.5699</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9375</v>
+        <v>-0.6437</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0561</v>
+        <v>-0.206</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8814</v>
+        <v>-0.4377</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.4469</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.485</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9859</v>
+        <v>-0.0317</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4303</v>
+        <v>-0.023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5556</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,31 +1189,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2105</v>
+        <v>-1.1634</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.583</v>
+        <v>0.1435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3725</v>
+        <v>-1.3069</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8262</v>
+        <v>0.4493</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8338</v>
+        <v>0.2234</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0076</v>
+        <v>0.2258</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4699</v>
+        <v>1.093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0398</v>
+        <v>0.4294</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5699</v>
+        <v>0.6635</v>
       </c>
       <c r="M10" t="n">
         <v>-0.6437</v>
@@ -1225,37 +1225,37 @@
         <v>-0.4377</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1838</v>
+        <v>-0.1685</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.023</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0898</v>
+        <v>-0.1455</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5617</v>
+        <v>-1.3334</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.107</v>
+        <v>-3.3555</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4546</v>
+        <v>2.0221</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4493</v>
+        <v>-2.0842</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2234</v>
+        <v>0.1491</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2258</v>
+        <v>-2.2333</v>
       </c>
       <c r="J11" t="n">
-        <v>1.093</v>
+        <v>-0.6579</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4294</v>
+        <v>0.5234</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6635</v>
+        <v>-1.1813</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6437</v>
+        <v>-1.4263</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.206</v>
+        <v>-0.3743</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4377</v>
+        <v>-1.052</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5668</v>
+        <v>1.6772</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2736</v>
+        <v>1.0082</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2932</v>
+        <v>0.669</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.631</v>
+        <v>-1.6642</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0457</v>
+        <v>-2.1528</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4147</v>
+        <v>0.4886</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2931</v>
@@ -1390,13 +1390,13 @@
         <v>3.1499</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.376</v>
+        <v>0.5907</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9849</v>
+        <v>-0.092</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6088</v>
+        <v>0.6827</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.722399999999999</v>
+        <v>4.543299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2497</v>
+        <v>2.0705</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4728</v>
+        <v>2.4729</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9149000000000003</v>
+        <v>0.9148999999999994</v>
       </c>
       <c r="H13" t="n">
-        <v>1.03</v>
+        <v>1.029999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1149999999999987</v>
+        <v>-0.1149999999999992</v>
       </c>
       <c r="J13" t="n">
         <v>18.1683</v>
@@ -1459,7 +1459,7 @@
         <v>-9.636999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9262999999999995</v>
+        <v>0.9262999999999996</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.3814</v>
@@ -1468,10 +1468,10 @@
         <v>21.3079</v>
       </c>
       <c r="S13" t="n">
-        <v>4.085199999999999</v>
+        <v>4.9058</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3108000000000007</v>
+        <v>0.5101</v>
       </c>
       <c r="U13" t="n">
         <v>4.395799999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.096</v>
+        <v>5.1929</v>
       </c>
       <c r="E14" t="n">
-        <v>4.939</v>
+        <v>5.2328</v>
       </c>
       <c r="F14" t="n">
-        <v>0.157</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" t="n">
         <v>2.111</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6623</v>
+        <v>-0.5655</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.766</v>
+        <v>-0.4722</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1037</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.4621</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5356</v>
+        <v>3.5838</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0874</v>
+        <v>3.2832</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4483</v>
+        <v>0.3005</v>
       </c>
       <c r="G15" t="n">
         <v>2.4906</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5113</v>
+        <v>-0.4632</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0943</v>
+        <v>-0.8984</v>
       </c>
       <c r="U15" t="n">
-        <v>0.583</v>
+        <v>0.4352</v>
       </c>
       <c r="V15" t="n">
         <v>0.63</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5883</v>
+        <v>1.8802</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5883</v>
+        <v>1.0853</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5883</v>
+        <v>1.6775</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.1932</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6221</v>
+        <v>1.8707</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5883</v>
+        <v>3.6233</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.8542</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6221</v>
+        <v>2.7691</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.9458</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.0474</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.8984</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.7026</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.0386</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.233</v>
+        <v>1.5883</v>
       </c>
       <c r="E17" t="n">
-        <v>0.346</v>
+        <v>1.5883</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8871</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6067</v>
+        <v>1.5883</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7264</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1197</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8334</v>
+        <v>1.5883</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3618</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5284</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2267</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6354</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5913</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1328</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1838</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.193</v>
+        <v>1.087</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6936</v>
+        <v>0.0522</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4995</v>
+        <v>1.0348</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6775</v>
+        <v>0.6067</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1932</v>
+        <v>1.7264</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8707</v>
+        <v>-1.1197</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6233</v>
+        <v>1.8334</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8542</v>
+        <v>2.3618</v>
       </c>
       <c r="L18" t="n">
-        <v>2.7691</v>
+        <v>-0.5284</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9458</v>
+        <v>-1.2267</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0474</v>
+        <v>-0.6354</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8984</v>
+        <v>-0.5913</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7793</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4283</v>
+        <v>-0.2789</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0943</v>
+        <v>-0.2428</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.334</v>
+        <v>-0.0361</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9439</v>
+        <v>0.9444</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7299</v>
+        <v>0.8273</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7716</v>
+        <v>0.9674</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0417</v>
+        <v>-0.1401</v>
       </c>
       <c r="G19" t="n">
         <v>2.1743</v>
@@ -1936,13 +1936,13 @@
         <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6302</v>
+        <v>-0.5329</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3019</v>
+        <v>-0.4004</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6289</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7202</v>
+        <v>0.4751</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0265</v>
+        <v>-0.1694</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6937</v>
+        <v>0.6445</v>
       </c>
       <c r="G20" t="n">
         <v>0.1975</v>
@@ -2014,13 +2014,13 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0219</v>
+        <v>-0.2232</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0838</v>
+        <v>-0.1331</v>
       </c>
       <c r="V20" t="n">
         <v>0.3155</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9036</v>
+        <v>-1.7565</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.822</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9837</v>
+        <v>-0.9345</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1617</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3713</v>
+        <v>-0.2241</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.043</v>
+        <v>0.0062</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.695</v>
+        <v>-2.7437</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0198</v>
+        <v>-3.1177</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3248</v>
+        <v>0.374</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5996</v>
@@ -2170,13 +2170,13 @@
         <v>3.3352</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4414</v>
+        <v>-0.5394</v>
       </c>
       <c r="U22" t="n">
-        <v>0.049</v>
+        <v>0.0982</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7094</v>
+        <v>-4.0278</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.692</v>
+        <v>-2.9858</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0173</v>
+        <v>-1.042</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4175</v>
@@ -2248,13 +2248,13 @@
         <v>2.9646</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0711</v>
+        <v>-0.3895</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.332</v>
+        <v>-0.6258</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2609</v>
+        <v>0.2363</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0104</v>
+        <v>-4.4514</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6603</v>
+        <v>-4.052</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3501</v>
+        <v>-0.3993</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5686</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4683</v>
+        <v>0.0274</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1604</v>
+        <v>-0.2313</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3079</v>
+        <v>0.2586</v>
       </c>
       <c r="V24" t="n">
         <v>0.3133</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5004</v>
+        <v>-5.3778</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6331</v>
+        <v>-3.5352</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8673</v>
+        <v>-1.8426</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0133</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3753</v>
+        <v>-0.2528</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.047</v>
+        <v>-0.0224</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.722800000000001</v>
+        <v>-3.7226</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4727</v>
+        <v>-2.472899999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2497</v>
+        <v>-1.2498</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9148000000000005</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0298</v>
+        <v>-1.029800000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1151000000000011</v>
+        <v>0.1151000000000002</v>
       </c>
       <c r="J26" t="n">
         <v>17.2534</v>
@@ -2485,13 +2485,13 @@
         <v>-4.0849</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.395799999999999</v>
+        <v>-4.3958</v>
       </c>
       <c r="U26" t="n">
-        <v>0.311</v>
+        <v>0.3106</v>
       </c>
       <c r="V26" t="n">
-        <v>2.203600000000001</v>
+        <v>2.203600000000002</v>
       </c>
       <c r="W26" t="n">
         <v>5.977600000000001</v>
